--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,6 +29,10 @@
     <font>
       <b val="1"/>
       <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
     </font>
     <font>
       <b val="1"/>
@@ -79,10 +83,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -456,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -476,192 +481,162 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>PROVISIONAL — column D 'What needs to change' is pending a fresh LIVE staging check (needs current cookies); it will be rewritten to observed build behaviour before sign-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>The other 174 cases need no change (167 Verified, 21 Blocked-on-environment, 1 to re-verify live, 4 retired). Note: the Fees &amp; Discounts V1 stories are still Open in Jira even though the feature is live, so most rows below wait on an open ticket. Nothing pushed to TestRail yet.  Orange rows = waiting on a ticket that is NOT yet done.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Case ID</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>TestRail link</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>What needs to change</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Driving ticket</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Ticket status</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Action</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>TestRail link</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>What needs to change</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Driving ticket</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Ticket status</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>C28436</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Confirm which permission controls adding or editing a whole-work-order fee/discount — the build may use one single 'edit work order' check instead of the separate whole-WO and line-level permissions the spec describes. Needs a check on staging with a restricted user.</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>SV-8277 / SV-8289</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>C28456</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Inline display (Lines tab)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>On a labour line with two or more fees/discounts the build shows every row and has NO 'Show more / Show less' collapse control the spec asks for. Confirmed difference — decide whether to change the case to match the build or log a fix for the build.</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>SV-8279 / SV-8288</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>C28460</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>The Statistics tab shows fees/discounts as one combined total with no per-item rows, so there is no per-item link to jump to the item. Confirmed difference from the design — decide keep-as-is or log a fix.</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>C28462</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Statistics tab</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>SV-8280</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
@@ -670,294 +645,331 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>C28462</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Statistics tab</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>SV-8280</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
           <t>C30618</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/30618</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Labor-line Fee/Discount</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>The 'Add Labor Fee / Discount' label is correct, but the three-dot menu shows to the RIGHT of 'Unassigned' and should be on the LEFT. A fix is expected (this is why the ticket re-opened) — re-check the LEFT position on staging, then update the case.</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>SV-8479</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>C28489</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>On the customer Fees &amp; Discounts tab the 'add template' dropdown lists the template NAME only (no Type/Calc/Amount columns), and a Processing Fee shows as 'Fee'. Confirm the accepted display and update the case wording to match the build.</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>SV-8284 / SV-8285</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>C28490</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>SV-8285</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>C28511</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Template admin — scoping</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>On a single labour/part line there is NO 'Apply from template' picker at all, so the template-scoping rule can't be exercised at line level (the picker only exists on the whole work-order dialog). Confirm and adjust the case's scope.</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>SV-8278 / SV-8281</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>C28526</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Processing Fee — WO behavior</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>SV-8279 / SV-8284</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>C28527</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>The processing-fee amount is worked out on the wrong base — it includes the whole-work-order fees and their tax, when the spec says to leave those out. Confirmed calculation defect — log the fix; the case stays as-is and will correctly fail until it's fixed.</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>SV-8284</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>C28580</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Same processing-fee base problem as C28527 in the overall calculation check — the grand-total base wrongly includes whole-work-order fees and their tax. Confirmed calculation defect — log the fix.</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>SV-7865</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>NOT DONE (Testing QA)</t>
         </is>
       </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>C28586</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>SV-8289</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
@@ -1001,444 +1013,444 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Case ID</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>TestRail link</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>What needs to change</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Driving ticket</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Ticket status</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>C28436</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Whole-WO Fee/Discount</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Confirm which permission controls adding or editing a whole-work-order fee/discount — the build may use one single 'edit work order' check instead of the separate whole-WO and line-level permissions the spec describes. Needs a check on staging with a restricted user.</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>SV-8277 / SV-8289</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>C28456</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Inline display (Lines tab)</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>On a labour line with two or more fees/discounts the build shows every row and has NO 'Show more / Show less' collapse control the spec asks for. Confirmed difference — decide whether to change the case to match the build or log a fix for the build.</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>SV-8279 / SV-8288</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>C28460</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>The Statistics tab shows fees/discounts as one combined total with no per-item rows, so there is no per-item link to jump to the item. Confirmed difference from the design — decide keep-as-is or log a fix.</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>C28462</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>C28489</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>On the customer Fees &amp; Discounts tab the 'add template' dropdown lists the template NAME only (no Type/Calc/Amount columns), and a Processing Fee shows as 'Fee'. Confirm the accepted display and update the case wording to match the build.</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>SV-8284 / SV-8285</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>C28490</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>SV-8285</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>C28511</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Template admin — scoping</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>On a single labour/part line there is NO 'Apply from template' picker at all, so the template-scoping rule can't be exercised at line level (the picker only exists on the whole work-order dialog). Confirm and adjust the case's scope.</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>SV-8278 / SV-8281</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>C28526</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Processing Fee — WO behavior</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>SV-8279 / SV-8284</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>C28527</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>The processing-fee amount is worked out on the wrong base — it includes the whole-work-order fees and their tax, when the spec says to leave those out. Confirmed calculation defect — log the fix; the case stays as-is and will correctly fail until it's fixed.</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>SV-8284</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>C28580</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Same processing-fee base problem as C28527 in the overall calculation check — the grand-total base wrongly includes whole-work-order fees and their tax. Confirmed calculation defect — log the fix.</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>SV-7865</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>NOT DONE (Testing QA)</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>C28586</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Permissions (Story 13)</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>SV-8289</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>DECISION</t>
         </is>

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -39,7 +39,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,7 +98,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -483,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>PROVISIONAL — column D 'What needs to change' is pending a fresh LIVE staging check (needs current cookies); it will be rewritten to observed build behaviour before sign-off.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 2 of 12 rows re-verified live on staging (green); the rest are flagged '⏳ LIVE CHECK PENDING' in column D and still need live observation.</t>
         </is>
       </c>
     </row>
@@ -549,7 +554,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Confirm which permission controls adding or editing a whole-work-order fee/discount — the build may use one single 'edit work order' check instead of the separate whole-WO and line-level permissions the spec describes. Needs a check on staging with a restricted user.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Confirm which permission controls adding or editing a whole-work-order fee/discount — the build may use one single 'edit work order' check instead of the separate whole-WO and line-level permissions the spec describes. Needs a check on staging with a restricted user.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -569,39 +574,39 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>C28456</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Inline display (Lines tab)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>On a labour line with two or more fees/discounts the build shows every row and has NO 'Show more / Show less' collapse control the spec asks for. Confirmed difference — decide whether to change the case to match the build or log a fix for the build.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23: a labor line with 2+ fees/discounts now shows an inline 'Fee 10% +$46.49' row PLUS a 'Show 1 more' / 'Show less' collapse-expand toggle (clicking expands then reads 'Show less'). The collapse control the spec asks for EXISTS — the earlier 'no Show more/less toggle' finding is resolved. Update the case to Verified.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>SV-8279 / SV-8288</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>
@@ -623,7 +628,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>The Statistics tab shows fees/discounts as one combined total with no per-item rows, so there is no per-item link to jump to the item. Confirmed difference from the design — decide keep-as-is or log a fix.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The Statistics tab shows fees/discounts as one combined total with no per-item rows, so there is no per-item link to jump to the item. Confirmed difference from the design — decide keep-as-is or log a fix.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -660,7 +665,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -697,7 +702,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>The 'Add Labor Fee / Discount' label is correct, but the three-dot menu shows to the RIGHT of 'Unassigned' and should be on the LEFT. A fix is expected (this is why the ticket re-opened) — re-check the LEFT position on staging, then update the case.</t>
+          <t>LIVE 2026-07-23: on the labor line, 'Unassigned' renders at x≈428 and the 'Add labor fee or discount' three-dot menu at x≈502 — i.e. the menu is to the RIGHT of 'Unassigned'; per SV-8479 item-1 it must be on the LEFT. Label is correct; position is still wrong — deviation stands, track the fix.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -734,7 +739,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>On the customer Fees &amp; Discounts tab the 'add template' dropdown lists the template NAME only (no Type/Calc/Amount columns), and a Processing Fee shows as 'Fee'. Confirm the accepted display and update the case wording to match the build.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On the customer Fees &amp; Discounts tab the 'add template' dropdown lists the template NAME only (no Type/Calc/Amount columns), and a Processing Fee shows as 'Fee'. Confirm the accepted display and update the case wording to match the build.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -771,7 +776,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -808,7 +813,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>On a single labour/part line there is NO 'Apply from template' picker at all, so the template-scoping rule can't be exercised at line level (the picker only exists on the whole work-order dialog). Confirm and adjust the case's scope.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On a single labour/part line there is NO 'Apply from template' picker at all, so the template-scoping rule can't be exercised at line level (the picker only exists on the whole work-order dialog). Confirm and adjust the case's scope.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -845,7 +850,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -882,7 +887,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>The processing-fee amount is worked out on the wrong base — it includes the whole-work-order fees and their tax, when the spec says to leave those out. Confirmed calculation defect — log the fix; the case stays as-is and will correctly fail until it's fixed.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The processing-fee amount is worked out on the wrong base — it includes the whole-work-order fees and their tax, when the spec says to leave those out. Confirmed calculation defect — log the fix; the case stays as-is and will correctly fail until it's fixed.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -919,7 +924,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Same processing-fee base problem as C28527 in the overall calculation check — the grand-total base wrongly includes whole-work-order fees and their tax. Confirmed calculation defect — log the fix.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Same processing-fee base problem as C28527 in the overall calculation check — the grand-total base wrongly includes whole-work-order fees and their tax. Confirmed calculation defect — log the fix.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -956,7 +961,7 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1067,7 +1072,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Confirm which permission controls adding or editing a whole-work-order fee/discount — the build may use one single 'edit work order' check instead of the separate whole-WO and line-level permissions the spec describes. Needs a check on staging with a restricted user.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Confirm which permission controls adding or editing a whole-work-order fee/discount — the build may use one single 'edit work order' check instead of the separate whole-WO and line-level permissions the spec describes. Needs a check on staging with a restricted user.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1087,39 +1092,39 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>C28456</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Inline display (Lines tab)</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>On a labour line with two or more fees/discounts the build shows every row and has NO 'Show more / Show less' collapse control the spec asks for. Confirmed difference — decide whether to change the case to match the build or log a fix for the build.</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23: a labor line with 2+ fees/discounts now shows an inline 'Fee 10% +$46.49' row PLUS a 'Show 1 more' / 'Show less' collapse-expand toggle (clicking expands then reads 'Show less'). The collapse control the spec asks for EXISTS — the earlier 'no Show more/less toggle' finding is resolved. Update the case to Verified.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>SV-8279 / SV-8288</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1146,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>The Statistics tab shows fees/discounts as one combined total with no per-item rows, so there is no per-item link to jump to the item. Confirmed difference from the design — decide keep-as-is or log a fix.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The Statistics tab shows fees/discounts as one combined total with no per-item rows, so there is no per-item link to jump to the item. Confirmed difference from the design — decide keep-as-is or log a fix.</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -1178,7 +1183,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -1215,7 +1220,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>On the customer Fees &amp; Discounts tab the 'add template' dropdown lists the template NAME only (no Type/Calc/Amount columns), and a Processing Fee shows as 'Fee'. Confirm the accepted display and update the case wording to match the build.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On the customer Fees &amp; Discounts tab the 'add template' dropdown lists the template NAME only (no Type/Calc/Amount columns), and a Processing Fee shows as 'Fee'. Confirm the accepted display and update the case wording to match the build.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1252,7 +1257,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -1289,7 +1294,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>On a single labour/part line there is NO 'Apply from template' picker at all, so the template-scoping rule can't be exercised at line level (the picker only exists on the whole work-order dialog). Confirm and adjust the case's scope.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On a single labour/part line there is NO 'Apply from template' picker at all, so the template-scoping rule can't be exercised at line level (the picker only exists on the whole work-order dialog). Confirm and adjust the case's scope.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1326,7 +1331,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1363,7 +1368,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>The processing-fee amount is worked out on the wrong base — it includes the whole-work-order fees and their tax, when the spec says to leave those out. Confirmed calculation defect — log the fix; the case stays as-is and will correctly fail until it's fixed.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The processing-fee amount is worked out on the wrong base — it includes the whole-work-order fees and their tax, when the spec says to leave those out. Confirmed calculation defect — log the fix; the case stays as-is and will correctly fail until it's fixed.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1400,7 +1405,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Same processing-fee base problem as C28527 in the overall calculation check — the grand-total base wrongly includes whole-work-order fees and their tax. Confirmed calculation defect — log the fix.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Same processing-fee base problem as C28527 in the overall calculation check — the grand-total base wrongly includes whole-work-order fees and their tax. Confirmed calculation defect — log the fix.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1437,7 +1442,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Change list (12)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Change list (14)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Waiting on open tickets" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -466,6 +466,605 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fees and Discounts spec-recheck — cases that need a change or a decision (14 of 186).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-BUILD CHECK 2026-07-23: 4 of 14 rows re-verified live on staging (green); the rest are flagged '⏳ LIVE CHECK PENDING' in column D and still need live observation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>The other 174 cases need no change (167 Verified, 21 Blocked-on-environment, 1 to re-verify live, 4 retired). Note: the Fees &amp; Discounts V1 stories are still Open in Jira even though the feature is live, so most rows below wait on an open ticket. Nothing pushed to TestRail yet.  Orange rows = waiting on a ticket that is NOT yet done.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>TestRail link</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>What needs to change</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Driving ticket</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Ticket status</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>C28436</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Confirm which permission controls adding or editing a whole-work-order fee/discount — the build may use one single 'edit work order' check instead of the separate whole-WO and line-level permissions the spec describes. Needs a check on staging with a restricted user.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>SV-8277 / SV-8289</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>C28456</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Inline display (Lines tab)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23: a labor line with 2+ fees/discounts now shows an inline 'Fee 10% +$46.49' row PLUS a 'Show 1 more' / 'Show less' collapse-expand toggle (clicking expands then reads 'Show less'). The collapse control the spec asks for EXISTS — the earlier 'no Show more/less toggle' finding is resolved. Update the case to Verified.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>SV-8279 / SV-8288</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>C28460</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Statistics tab</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23: the Statistics tab now shows a 'Fees &amp; Discounts (6)' section with PER-ADJUSTMENT rows (columns % and Amount: 'Fee +10% +$46.49', 'Discount', 'Fee −11% −$2.39', etc.) plus a Total — the earlier 'aggregate only, no per-row' finding no longer holds. Still to confirm: whether each row has a scope hyperlink to jump to its item. Update the case to the per-row layout.</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>SV-8280</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>C28462</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Statistics tab</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>SV-8280</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>C30618</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30618</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Labor-line Fee/Discount</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23: on the labor line, 'Unassigned' renders at x≈428 and the 'Add labor fee or discount' three-dot menu at x≈502 — i.e. the menu is to the RIGHT of 'Unassigned'; per SV-8479 item-1 it must be on the LEFT. Label is correct; position is still wrong — deviation stands, track the fix.</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>SV-8479</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>C28489</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Customer Fees &amp; Discounts tab</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On the customer Fees &amp; Discounts tab the 'add template' dropdown lists the template NAME only (no Type/Calc/Amount columns), and a Processing Fee shows as 'Fee'. Confirm the accepted display and update the case wording to match the build.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>SV-8284 / SV-8285</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Apply update</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>C28490</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Customer Fees &amp; Discounts tab</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>SV-8285</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Apply update</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>C28511</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Template admin — scoping</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On a single labour/part line there is NO 'Apply from template' picker at all, so the template-scoping rule can't be exercised at line level (the picker only exists on the whole work-order dialog). Confirm and adjust the case's scope.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>SV-8278 / SV-8281</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>C28526</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Processing Fee — WO behavior</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>SV-8279 / SV-8284</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>C28527</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Processing Fee — calculation</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The processing-fee amount is worked out on the wrong base — it includes the whole-work-order fees and their tax, when the spec says to leave those out. Confirmed calculation defect — log the fix; the case stays as-is and will correctly fail until it's fixed.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>SV-8284</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>C28580</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Calculation contract</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Same processing-fee base problem as C28527 in the overall calculation check — the grand-total base wrongly includes whole-work-order fees and their tax. Confirmed calculation defect — log the fix.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>SV-7865</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Testing QA)</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>C28586</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Permissions (Story 13)</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>SV-8289</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>new (SV-8521)</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>(no TestRail case yet — to author)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Finance/Invoice — part-line display</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S9-25393 Finance/Estimate view): part-line adjustments DO render as indented child rows under their part — '↳ Name $11.00' and '↳ Fee (% of parts) ($2.39)' show under the T-BOLT CLAMP part, exactly like the labour-line '↳ Fee (% of labor)' / '↳ Discount'. So on the work-order invoice this appears FIXED (matches SV-8521 'Ready for QA'). Still to confirm: the Parts Sale invoice view. Author a case for both surfaces.</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>SV-8521</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Ready for QA)</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>New case + verify</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>new (SV-8520)</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>(no TestRail case yet — to author)</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Part line — display after receive/pick</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A fee on a PART line should stay visible on the line row after the part is received or picked; it currently disappears from the line (still correct in totals and on the invoice). Needs a new case covering line display staying in sync after receive/pick.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>SV-8520</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Testing Stage)</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>New case + verify</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -481,122 +1080,152 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fees and Discounts spec-recheck — cases that need a change or a decision (12 of 186).</t>
+          <t>Cases whose change depends on a ticket that is NOT yet done</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 2 of 12 rows re-verified live on staging (green); the rest are flagged '⏳ LIVE CHECK PENDING' in column D and still need live observation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>The other 174 cases need no change (167 Verified, 21 Blocked-on-environment, 1 to re-verify live, 4 retired). Note: the Fees &amp; Discounts V1 stories are still Open in Jira even though the feature is live, so most rows below wait on an open ticket. Nothing pushed to TestRail yet.  Orange rows = waiting on a ticket that is NOT yet done.</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>These should NOT be finalised until the ticket ships; keep the case tracking the target and re-verify after the fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Case ID</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>TestRail link</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>What needs to change</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Driving ticket</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Ticket status</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Action</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Case ID</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>TestRail link</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>What needs to change</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Driving ticket</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Ticket status</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Action</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>C28436</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Whole-WO Fee/Discount</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Confirm which permission controls adding or editing a whole-work-order fee/discount — the build may use one single 'edit work order' check instead of the separate whole-WO and line-level permissions the spec describes. Needs a check on staging with a restricted user.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>SV-8277 / SV-8289</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>C28436</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Confirm which permission controls adding or editing a whole-work-order fee/discount — the build may use one single 'edit work order' check instead of the separate whole-WO and line-level permissions the spec describes. Needs a check on staging with a restricted user.</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>SV-8277 / SV-8289</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>C28456</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Inline display (Lines tab)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23: a labor line with 2+ fees/discounts now shows an inline 'Fee 10% +$46.49' row PLUS a 'Show 1 more' / 'Show less' collapse-expand toggle (clicking expands then reads 'Show less'). The collapse control the spec asks for EXISTS — the earlier 'no Show more/less toggle' finding is resolved. Update the case to Verified.</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>SV-8279 / SV-8288</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>C28456</t>
+          <t>C28460</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Inline display (Lines tab)</t>
+          <t>Statistics tab</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>LIVE 2026-07-23: a labor line with 2+ fees/discounts now shows an inline 'Fee 10% +$46.49' row PLUS a 'Show 1 more' / 'Show less' collapse-expand toggle (clicking expands then reads 'Show less'). The collapse control the spec asks for EXISTS — the earlier 'no Show more/less toggle' finding is resolved. Update the case to Verified.</t>
+          <t>LIVE 2026-07-23: the Statistics tab now shows a 'Fees &amp; Discounts (6)' section with PER-ADJUSTMENT rows (columns % and Amount: 'Fee +10% +$46.49', 'Discount', 'Fee −11% −$2.39', etc.) plus a Total — the earlier 'aggregate only, no per-row' finding no longer holds. Still to confirm: whether each row has a scope hyperlink to jump to its item. Update the case to the per-row layout.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>SV-8279 / SV-8288</t>
+          <t>SV-8280</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -613,12 +1242,12 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>C28460</t>
+          <t>C28462</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -628,7 +1257,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The Statistics tab shows fees/discounts as one combined total with no per-item rows, so there is no per-item link to jump to the item. Confirmed difference from the design — decide keep-as-is or log a fix.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -650,27 +1279,27 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>C28462</t>
+          <t>C28489</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Statistics tab</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On the customer Fees &amp; Discounts tab the 'add template' dropdown lists the template NAME only (no Type/Calc/Amount columns), and a Processing Fee shows as 'Fee'. Confirm the accepted display and update the case wording to match the build.</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>SV-8280</t>
+          <t>SV-8284 / SV-8285</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -680,42 +1309,42 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>C30618</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30618</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Labor-line Fee/Discount</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23: on the labor line, 'Unassigned' renders at x≈428 and the 'Add labor fee or discount' three-dot menu at x≈502 — i.e. the menu is to the RIGHT of 'Unassigned'; per SV-8479 item-1 it must be on the LEFT. Label is correct; position is still wrong — deviation stands, track the fix.</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>SV-8479</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>C28490</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Customer Fees &amp; Discounts tab</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>SV-8285</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
@@ -724,27 +1353,27 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>C28489</t>
+          <t>C28511</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Template admin — scoping</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On the customer Fees &amp; Discounts tab the 'add template' dropdown lists the template NAME only (no Type/Calc/Amount columns), and a Processing Fee shows as 'Fee'. Confirm the accepted display and update the case wording to match the build.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On a single labour/part line there is NO 'Apply from template' picker at all, so the template-scoping rule can't be exercised at line level (the picker only exists on the whole work-order dialog). Confirm and adjust the case's scope.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>SV-8284 / SV-8285</t>
+          <t>SV-8278 / SV-8281</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -754,34 +1383,34 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Apply update</t>
+          <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>C28490</t>
+          <t>C28526</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Customer Fees &amp; Discounts tab</t>
+          <t>Processing Fee — WO behavior</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>SV-8285</t>
+          <t>SV-8279 / SV-8284</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -791,34 +1420,34 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Apply update</t>
+          <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>C28511</t>
+          <t>C28527</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Template admin — scoping</t>
+          <t>Processing Fee — calculation</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On a single labour/part line there is NO 'Apply from template' picker at all, so the template-scoping rule can't be exercised at line level (the picker only exists on the whole work-order dialog). Confirm and adjust the case's scope.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The processing-fee amount is worked out on the wrong base — it includes the whole-work-order fees and their tax, when the spec says to leave those out. Confirmed calculation defect — log the fix; the case stays as-is and will correctly fail until it's fixed.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>SV-8278 / SV-8281</t>
+          <t>SV-8284</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -835,32 +1464,32 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>C28526</t>
+          <t>C28580</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Processing Fee — WO behavior</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Same processing-fee base problem as C28527 in the overall calculation check — the grand-total base wrongly includes whole-work-order fees and their tax. Confirmed calculation defect — log the fix.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>SV-8279 / SV-8284</t>
+          <t>SV-7865</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>NOT DONE (Open)</t>
+          <t>NOT DONE (Testing QA)</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -872,27 +1501,27 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>C28527</t>
+          <t>C28586</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation</t>
+          <t>Permissions (Story 13)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The processing-fee amount is worked out on the wrong base — it includes the whole-work-order fees and their tax, when the spec says to leave those out. Confirmed calculation defect — log the fix; the case stays as-is and will correctly fail until it's fixed.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>SV-8284</t>
+          <t>SV-8289</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -907,557 +1536,76 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>C28580</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Same processing-fee base problem as C28527 in the overall calculation check — the grand-total base wrongly includes whole-work-order fees and their tax. Confirmed calculation defect — log the fix.</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>SV-7865</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Testing QA)</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>new (SV-8521)</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>(no TestRail case yet — to author)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Finance/Invoice — part-line display</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S9-25393 Finance/Estimate view): part-line adjustments DO render as indented child rows under their part — '↳ Name $11.00' and '↳ Fee (% of parts) ($2.39)' show under the T-BOLT CLAMP part, exactly like the labour-line '↳ Fee (% of labor)' / '↳ Discount'. So on the work-order invoice this appears FIXED (matches SV-8521 'Ready for QA'). Still to confirm: the Parts Sale invoice view. Author a case for both surfaces.</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>SV-8521</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Ready for QA)</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>New case + verify</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>C28586</t>
+          <t>new (SV-8520)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+          <t>(no TestRail case yet — to author)</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Permissions (Story 13)</t>
+          <t>Part line — display after receive/pick</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A fee on a PART line should stay visible on the line row after the part is received or picked; it currently disappears from the line (still correct in totals and on the invoice). Needs a new case covering line display staying in sync after receive/pick.</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>SV-8289</t>
+          <t>SV-8520</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>NOT DONE (Open)</t>
+          <t>NOT DONE (Testing Stage)</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="72" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cases whose change depends on a ticket that is NOT yet done</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>These should NOT be finalised until the ticket ships; keep the case tracking the target and re-verify after the fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Case ID</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>TestRail link</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Area</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>What needs to change</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Driving ticket</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Ticket status</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>C28436</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28436</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Whole-WO Fee/Discount</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Confirm which permission controls adding or editing a whole-work-order fee/discount — the build may use one single 'edit work order' check instead of the separate whole-WO and line-level permissions the spec describes. Needs a check on staging with a restricted user.</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>SV-8277 / SV-8289</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>C28456</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Inline display (Lines tab)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23: a labor line with 2+ fees/discounts now shows an inline 'Fee 10% +$46.49' row PLUS a 'Show 1 more' / 'Show less' collapse-expand toggle (clicking expands then reads 'Show less'). The collapse control the spec asks for EXISTS — the earlier 'no Show more/less toggle' finding is resolved. Update the case to Verified.</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>SV-8279 / SV-8288</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Apply update</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>C28460</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Statistics tab</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The Statistics tab shows fees/discounts as one combined total with no per-item rows, so there is no per-item link to jump to the item. Confirmed difference from the design — decide keep-as-is or log a fix.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>SV-8280</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>C28462</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Statistics tab</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>SV-8280</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>C28489</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Customer Fees &amp; Discounts tab</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On the customer Fees &amp; Discounts tab the 'add template' dropdown lists the template NAME only (no Type/Calc/Amount columns), and a Processing Fee shows as 'Fee'. Confirm the accepted display and update the case wording to match the build.</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>SV-8284 / SV-8285</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Apply update</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>C28490</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Customer Fees &amp; Discounts tab</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>SV-8285</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Apply update</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>C28511</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Template admin — scoping</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On a single labour/part line there is NO 'Apply from template' picker at all, so the template-scoping rule can't be exercised at line level (the picker only exists on the whole work-order dialog). Confirm and adjust the case's scope.</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>SV-8278 / SV-8281</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>C28526</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Processing Fee — WO behavior</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>SV-8279 / SV-8284</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>C28527</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Processing Fee — calculation</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The processing-fee amount is worked out on the wrong base — it includes the whole-work-order fees and their tax, when the spec says to leave those out. Confirmed calculation defect — log the fix; the case stays as-is and will correctly fail until it's fixed.</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>SV-8284</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>C28580</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Same processing-fee base problem as C28527 in the overall calculation check — the grand-total base wrongly includes whole-work-order fees and their tax. Confirmed calculation defect — log the fix.</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>SV-7865</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Testing QA)</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>C28586</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Permissions (Story 13)</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>SV-8289</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+          <t>New case + verify</t>
         </is>
       </c>
     </row>

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 4 of 14 rows re-verified live on staging (green); the rest are flagged '⏳ LIVE CHECK PENDING' in column D and still need live observation.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 5 of 14 rows re-verified live on staging (green); the rest are flagged '⏳ LIVE CHECK PENDING' in column D and still need live observation.</t>
         </is>
       </c>
     </row>
@@ -722,37 +722,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>C28489</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On the customer Fees &amp; Discounts tab the 'add template' dropdown lists the template NAME only (no Type/Calc/Amount columns), and a Processing Fee shows as 'Fee'. Confirm the accepted display and update the case wording to match the build.</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (customer 'Default Fees &amp; Discounts' tab): the defaults TABLE shows full columns — Name, Type, Calculation Type, Amount, Max Amount, Taxable — and a Processing Fee displays with Type 'Fee' (e.g. 'Processing Fee | Fee | % of Grand Total | 6%'), confirming the 'shows as Fee' point. Still to confirm: whether the 'Add Fee/Discount' picker DROPDOWN lists name-only vs columns. Update the case to the observed table display.</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>SV-8284 / SV-8285</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
@@ -1277,37 +1277,37 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>C28489</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On the customer Fees &amp; Discounts tab the 'add template' dropdown lists the template NAME only (no Type/Calc/Amount columns), and a Processing Fee shows as 'Fee'. Confirm the accepted display and update the case wording to match the build.</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (customer 'Default Fees &amp; Discounts' tab): the defaults TABLE shows full columns — Name, Type, Calculation Type, Amount, Max Amount, Taxable — and a Processing Fee displays with Type 'Fee' (e.g. 'Processing Fee | Fee | % of Grand Total | 6%'), confirming the 'shows as Fee' point. Still to confirm: whether the 'Add Fee/Discount' picker DROPDOWN lists name-only vs columns. Update the case to the observed table display.</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>SV-8284 / SV-8285</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 5 of 14 rows re-verified live on staging (green); the rest are flagged '⏳ LIVE CHECK PENDING' in column D and still need live observation.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 5 of 14 rows re-verified live on staging (green); 2 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The processing-fee amount is worked out on the wrong base — it includes the whole-work-order fees and their tax, when the spec says to leave those out. Confirmed calculation defect — log the fix; the case stays as-is and will correctly fail until it's fixed.</t>
+          <t>LIVE 2026-07-23: created a WO for a customer carrying default processing fees — the 5% and 6% processing_fee (calculationType pct_grand_total) AUTO-APPLIED alongside a whole-WO Flat Fee $11 (confirmed via API, appliedBy=customer_default). The definitive base-inclusion check (does the processing-fee base wrongly include the whole-WO fee?) needs a priced line so the fees resolve above $0 — but adding a line returns HTTP 500 (WO line-create env defect, requestId e1069cd9…) and the UI line-add hits the async ShopCoach builder. CHARACTERISED-BLOCKED on the line-create 500; retest when fixed.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Same processing-fee base problem as C28527 in the overall calculation check — the grand-total base wrongly includes whole-work-order fees and their tax. Confirmed calculation defect — log the fix.</t>
+          <t>LIVE 2026-07-23: same as C28527 — customer-default processing fees (5%/6% of Grand Total) auto-apply with a whole-WO Flat Fee (confirmed via API); the base-inclusion calc can't be resolved because adding a priced line returns HTTP 500 (WO line-create env defect, requestId e1069cd9…). CHARACTERISED-BLOCKED; retest when the 500 is fixed.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: The processing-fee amount is worked out on the wrong base — it includes the whole-work-order fees and their tax, when the spec says to leave those out. Confirmed calculation defect — log the fix; the case stays as-is and will correctly fail until it's fixed.</t>
+          <t>LIVE 2026-07-23: created a WO for a customer carrying default processing fees — the 5% and 6% processing_fee (calculationType pct_grand_total) AUTO-APPLIED alongside a whole-WO Flat Fee $11 (confirmed via API, appliedBy=customer_default). The definitive base-inclusion check (does the processing-fee base wrongly include the whole-WO fee?) needs a priced line so the fees resolve above $0 — but adding a line returns HTTP 500 (WO line-create env defect, requestId e1069cd9…) and the UI line-add hits the async ShopCoach builder. CHARACTERISED-BLOCKED on the line-create 500; retest when fixed.</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Same processing-fee base problem as C28527 in the overall calculation check — the grand-total base wrongly includes whole-work-order fees and their tax. Confirmed calculation defect — log the fix.</t>
+          <t>LIVE 2026-07-23: same as C28527 — customer-default processing fees (5%/6% of Grand Total) auto-apply with a whole-WO Flat Fee (confirmed via API); the base-inclusion calc can't be resolved because adding a priced line returns HTTP 500 (WO line-create env defect, requestId e1069cd9…). CHARACTERISED-BLOCKED; retest when the 500 is fixed.</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 5 of 14 rows re-verified live on staging (green); 2 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 9 of 14 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
         </is>
       </c>
     </row>
@@ -796,39 +796,39 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>C28511</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Template admin — scoping</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On a single labour/part line there is NO 'Apply from template' picker at all, so the template-scoping rule can't be exercised at line level (the picker only exists on the whole work-order dialog). Confirm and adjust the case's scope.</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23: the LINE-SCOPE fee dialog now HAS a template picker — the 'New Part Fee / Discount' dialog (and the labour-line one) shows 'Apply From Template' with 'Showing templates compatible with this line', and the whole-WO dialog has it too. The earlier 'no template picker at line scope' deviation is resolved; the scope-filtering hint is present. Update the case to the picker-present, scope-filtered behaviour.</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>SV-8278 / SV-8281</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>
@@ -870,76 +870,76 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>C28527</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23: created a WO for a customer carrying default processing fees — the 5% and 6% processing_fee (calculationType pct_grand_total) AUTO-APPLIED alongside a whole-WO Flat Fee $11 (confirmed via API, appliedBy=customer_default). The definitive base-inclusion check (does the processing-fee base wrongly include the whole-WO fee?) needs a priced line so the fees resolve above $0 — but adding a line returns HTTP 500 (WO line-create env defect, requestId e1069cd9…) and the UI line-add hits the async ShopCoach builder. CHARACTERISED-BLOCKED on the line-create 500; retest when fixed.</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25989, seeded by QA): processing-fee base now EXCLUDES whole-WO fees — FIXED. Numbers: labour $244 + shop supplies $20 = net subtotal $264; ×1.05 GST = Grand Total $277.20; Processing Fee 10% = $27.72 (matches the observed $27.72 to the cent). The whole-WO 'bil' fee ($24.40) is NOT in the base (the old bug would give $30.28). Spec §5-R4 satisfied — the earlier 'base includes whole-WO fees' deviation is resolved. Update the case to Verified.</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>SV-8284</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>C28580</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23: same as C28527 — customer-default processing fees (5%/6% of Grand Total) auto-apply with a whole-WO Flat Fee (confirmed via API); the base-inclusion calc can't be resolved because adding a priced line returns HTTP 500 (WO line-create env defect, requestId e1069cd9…). CHARACTERISED-BLOCKED; retest when the 500 is fixed.</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25989): same result as C28527 — the Grand-Total base for the Processing Fee correctly excludes whole-WO fees and their tax (10% × ($264 net ×1.05) = $27.72, observed $27.72; buggy would be $30.28). Calculation-contract deviation resolved. Update the case to Verified.</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>SV-7865</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>NOT DONE (Testing QA)</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>
@@ -1018,37 +1018,37 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>new (SV-8520)</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>(no TestRail case yet — to author)</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Part line — display after receive/pick</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A fee on a PART line should stay visible on the line row after the part is received or picked; it currently disappears from the line (still correct in totals and on the invoice). Needs a new case covering line display staying in sync after receive/pick.</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25991, QA-seeded): CONFIRMED — a 50% part fee was added to a part then the part was picked; the part line row now shows $99.00 with NO indented fee child row, yet the line TOTAL is $392.50 (labour $244 + part $99 + the $49.50 fee). So the fee is still billed but hidden from the line after pick — matches SV-8520. Author the case as a confirmed defect (Testing Stage).</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>SV-8520</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>NOT DONE (Testing Stage)</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>New case + verify</t>
         </is>
@@ -1351,39 +1351,39 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>C28511</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Template admin — scoping</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: On a single labour/part line there is NO 'Apply from template' picker at all, so the template-scoping rule can't be exercised at line level (the picker only exists on the whole work-order dialog). Confirm and adjust the case's scope.</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23: the LINE-SCOPE fee dialog now HAS a template picker — the 'New Part Fee / Discount' dialog (and the labour-line one) shows 'Apply From Template' with 'Showing templates compatible with this line', and the whole-WO dialog has it too. The earlier 'no template picker at line scope' deviation is resolved; the scope-filtering hint is present. Update the case to the picker-present, scope-filtered behaviour.</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>SV-8278 / SV-8281</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>
@@ -1425,76 +1425,76 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>C28527</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23: created a WO for a customer carrying default processing fees — the 5% and 6% processing_fee (calculationType pct_grand_total) AUTO-APPLIED alongside a whole-WO Flat Fee $11 (confirmed via API, appliedBy=customer_default). The definitive base-inclusion check (does the processing-fee base wrongly include the whole-WO fee?) needs a priced line so the fees resolve above $0 — but adding a line returns HTTP 500 (WO line-create env defect, requestId e1069cd9…) and the UI line-add hits the async ShopCoach builder. CHARACTERISED-BLOCKED on the line-create 500; retest when fixed.</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25989, seeded by QA): processing-fee base now EXCLUDES whole-WO fees — FIXED. Numbers: labour $244 + shop supplies $20 = net subtotal $264; ×1.05 GST = Grand Total $277.20; Processing Fee 10% = $27.72 (matches the observed $27.72 to the cent). The whole-WO 'bil' fee ($24.40) is NOT in the base (the old bug would give $30.28). Spec §5-R4 satisfied — the earlier 'base includes whole-WO fees' deviation is resolved. Update the case to Verified.</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>SV-8284</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>C28580</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23: same as C28527 — customer-default processing fees (5%/6% of Grand Total) auto-apply with a whole-WO Flat Fee (confirmed via API); the base-inclusion calc can't be resolved because adding a priced line returns HTTP 500 (WO line-create env defect, requestId e1069cd9…). CHARACTERISED-BLOCKED; retest when the 500 is fixed.</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25989): same result as C28527 — the Grand-Total base for the Processing Fee correctly excludes whole-WO fees and their tax (10% × ($264 net ×1.05) = $27.72, observed $27.72; buggy would be $30.28). Calculation-contract deviation resolved. Update the case to Verified.</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>SV-7865</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>NOT DONE (Testing QA)</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>
@@ -1573,37 +1573,37 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>new (SV-8520)</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>(no TestRail case yet — to author)</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Part line — display after receive/pick</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A fee on a PART line should stay visible on the line row after the part is received or picked; it currently disappears from the line (still correct in totals and on the invoice). Needs a new case covering line display staying in sync after receive/pick.</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25991, QA-seeded): CONFIRMED — a 50% part fee was added to a part then the part was picked; the part line row now shows $99.00 with NO indented fee child row, yet the line TOTAL is $392.50 (labour $244 + part $99 + the $49.50 fee). So the fee is still billed but hidden from the line after pick — matches SV-8520. Author the case as a confirmed defect (Testing Stage).</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>SV-8520</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>NOT DONE (Testing Stage)</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>New case + verify</t>
         </is>

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Change list (14)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Change list (13)" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Waiting on open tickets" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -481,14 +481,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fees and Discounts spec-recheck — cases that need a change or a decision (14 of 186).</t>
+          <t>Fees and Discounts spec-recheck — cases that need a change or a decision (13 of 186).</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 9 of 14 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 8 of 13 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
         </is>
       </c>
     </row>
@@ -687,32 +687,32 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>C30618</t>
+          <t>C28489</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/30618</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Labor-line Fee/Discount</t>
+          <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>LIVE 2026-07-23: on the labor line, 'Unassigned' renders at x≈428 and the 'Add labor fee or discount' three-dot menu at x≈502 — i.e. the menu is to the RIGHT of 'Unassigned'; per SV-8479 item-1 it must be on the LEFT. Label is correct; position is still wrong — deviation stands, track the fix.</t>
+          <t>LIVE 2026-07-23 (customer 'Default Fees &amp; Discounts' tab): the defaults TABLE shows full columns — Name, Type, Calculation Type, Amount, Max Amount, Taxable — and a Processing Fee displays with Type 'Fee' (e.g. 'Processing Fee | Fee | % of Grand Total | 6%'), confirming the 'shows as Fee' point. Still to confirm: whether the 'Add Fee/Discount' picker DROPDOWN lists name-only vs columns. Update the case to the observed table display.</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>SV-8479</t>
+          <t>SV-8284 / SV-8285</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>DONE</t>
+          <t>NOT DONE (Open)</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -722,182 +722,182 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>C28489</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>C28490</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23 (customer 'Default Fees &amp; Discounts' tab): the defaults TABLE shows full columns — Name, Type, Calculation Type, Amount, Max Amount, Taxable — and a Processing Fee displays with Type 'Fee' (e.g. 'Processing Fee | Fee | % of Grand Total | 6%'), confirming the 'shows as Fee' point. Still to confirm: whether the 'Add Fee/Discount' picker DROPDOWN lists name-only vs columns. Update the case to the observed table display.</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>SV-8284 / SV-8285</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>SV-8285</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>C28490</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Customer Fees &amp; Discounts tab</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>SV-8285</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>C28511</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Template admin — scoping</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23: the LINE-SCOPE fee dialog now HAS a template picker — the 'New Part Fee / Discount' dialog (and the labour-line one) shows 'Apply From Template' with 'Showing templates compatible with this line', and the whole-WO dialog has it too. The earlier 'no template picker at line scope' deviation is resolved; the scope-filtering hint is present. Update the case to the picker-present, scope-filtered behaviour.</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>SV-8278 / SV-8281</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>C28511</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Template admin — scoping</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23: the LINE-SCOPE fee dialog now HAS a template picker — the 'New Part Fee / Discount' dialog (and the labour-line one) shows 'Apply From Template' with 'Showing templates compatible with this line', and the whole-WO dialog has it too. The earlier 'no template picker at line scope' deviation is resolved; the scope-filtering hint is present. Update the case to the picker-present, scope-filtered behaviour.</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>SV-8278 / SV-8281</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>C28526</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Processing Fee — WO behavior</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>SV-8279 / SV-8284</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>C28527</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Processing Fee — calculation</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25989, seeded by QA): processing-fee base now EXCLUDES whole-WO fees — FIXED. Numbers: labour $244 + shop supplies $20 = net subtotal $264; ×1.05 GST = Grand Total $277.20; Processing Fee 10% = $27.72 (matches the observed $27.72 to the cent). The whole-WO 'bil' fee ($24.40) is NOT in the base (the old bug would give $30.28). Spec §5-R4 satisfied — the earlier 'base includes whole-WO fees' deviation is resolved. Update the case to Verified.</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>SV-8284</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>Apply update</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>C28526</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Processing Fee — WO behavior</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>SV-8279 / SV-8284</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C28527</t>
+          <t>C28580</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Processing Fee — calculation</t>
+          <t>Calculation contract</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>LIVE 2026-07-23 (WO S-25989, seeded by QA): processing-fee base now EXCLUDES whole-WO fees — FIXED. Numbers: labour $244 + shop supplies $20 = net subtotal $264; ×1.05 GST = Grand Total $277.20; Processing Fee 10% = $27.72 (matches the observed $27.72 to the cent). The whole-WO 'bil' fee ($24.40) is NOT in the base (the old bug would give $30.28). Spec §5-R4 satisfied — the earlier 'base includes whole-WO fees' deviation is resolved. Update the case to Verified.</t>
+          <t>LIVE 2026-07-23 (WO S-25989): same result as C28527 — the Grand-Total base for the Processing Fee correctly excludes whole-WO fees and their tax (10% × ($264 net ×1.05) = $27.72, observed $27.72; buggy would be $30.28). Calculation-contract deviation resolved. Update the case to Verified.</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>SV-8284</t>
+          <t>SV-7865</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>NOT DONE (Open)</t>
+          <t>NOT DONE (Testing QA)</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
@@ -907,83 +907,83 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>C28580</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Calculation contract</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23 (WO S-25989): same result as C28527 — the Grand-Total base for the Processing Fee correctly excludes whole-WO fees and their tax (10% × ($264 net ×1.05) = $27.72, observed $27.72; buggy would be $30.28). Calculation-contract deviation resolved. Update the case to Verified.</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>SV-7865</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Testing QA)</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>Apply update</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>C28586</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Permissions (Story 13)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>SV-8289</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>DECISION</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>C28586</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/28586</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Permissions (Story 13)</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>SV-8289</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>new (SV-8521)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>(no TestRail case yet — to author)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Finance/Invoice — part-line display</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S9-25393 Finance/Estimate view): part-line adjustments DO render as indented child rows under their part — '↳ Name $11.00' and '↳ Fee (% of parts) ($2.39)' show under the T-BOLT CLAMP part, exactly like the labour-line '↳ Fee (% of labor)' / '↳ Discount'. So on the work-order invoice this appears FIXED (matches SV-8521 'Ready for QA'). Still to confirm: the Parts Sale invoice view. Author a case for both surfaces.</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>SV-8521</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Ready for QA)</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>New case + verify</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>new (SV-8521)</t>
+          <t>new (SV-8520)</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
@@ -993,62 +993,25 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Finance/Invoice — part-line display</t>
+          <t>Part line — display after receive/pick</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>LIVE 2026-07-23 (WO S9-25393 Finance/Estimate view): part-line adjustments DO render as indented child rows under their part — '↳ Name $11.00' and '↳ Fee (% of parts) ($2.39)' show under the T-BOLT CLAMP part, exactly like the labour-line '↳ Fee (% of labor)' / '↳ Discount'. So on the work-order invoice this appears FIXED (matches SV-8521 'Ready for QA'). Still to confirm: the Parts Sale invoice view. Author a case for both surfaces.</t>
+          <t>LIVE 2026-07-23 (WO S-25991, QA-seeded): CONFIRMED — a 50% part fee was added to a part then the part was picked; the part line row now shows $99.00 with NO indented fee child row, yet the line TOTAL is $392.50 (labour $244 + part $99 + the $49.50 fee). So the fee is still billed but hidden from the line after pick — matches SV-8520. Author the case as a confirmed defect (Testing Stage).</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>SV-8521</t>
+          <t>SV-8520</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>NOT DONE (Ready for QA)</t>
+          <t>NOT DONE (Testing Stage)</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>New case + verify</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>new (SV-8520)</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>(no TestRail case yet — to author)</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Part line — display after receive/pick</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23 (WO S-25991, QA-seeded): CONFIRMED — a 50% part fee was added to a part then the part was picked; the part line row now shows $99.00 with NO indented fee child row, yet the line TOTAL is $392.50 (labour $244 + part $99 + the $49.50 fee). So the fee is still billed but hidden from the line after pick — matches SV-8520. Author the case as a confirmed defect (Testing Stage).</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>SV-8520</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Testing Stage)</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>New case + verify</t>
         </is>

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 8 of 13 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 9 of 13 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
         </is>
       </c>
     </row>
@@ -648,39 +648,39 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>C28462</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25989 Statistics tab): fees/discounts are listed OLDEST-FIRST — display order Part Fee, WO Processing Fee, bil matches their creation order (createdAt 14:17:53, 14:17:53, 14:44:25). Matches spec §5-R9; the case (authored to spec) is correct. Part Fee correctly shows $0.00. Mark Verified.</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>
@@ -1203,39 +1203,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>C28462</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Wording check: the spec says work-order screens list fees/discounts oldest-first (the order they were created); an internal note said newest-first. The case was written to the spec (oldest-first) — confirm the actual order on staging.</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25989 Statistics tab): fees/discounts are listed OLDEST-FIRST — display order Part Fee, WO Processing Fee, bil matches their creation order (createdAt 14:17:53, 14:17:53, 14:44:25). Matches spec §5-R9; the case (authored to spec) is correct. Part Fee correctly shows $0.00. Mark Verified.</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 9 of 13 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 10 of 13 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
         </is>
       </c>
     </row>
@@ -796,39 +796,39 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>C28526</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Processing Fee — WO behavior</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25989): a processing fee is REMOVE-ONLY on the backend — POST /api/work-orders/adjustments/change on the processing fee returns HTTP 409 'A processing fee cannot be edited through this endpoint', while the same edit on a normal whole-WO fee returns 200. Backend behaviour matches spec S8-N5/S8-R17. The residual deviation is UI-only (the ⋮ menu still OFFERS 'Edit') — the per-fee ⋮ menu could not be isolated headless this run; re-confirm the menu label. Update the backend-enforcement part to Verified.</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>SV-8279 / SV-8284</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>
@@ -1351,39 +1351,39 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>C28526</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Processing Fee — WO behavior</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: A processing fee can't be edited (the backend blocks it), but the work-order ⋮ menu still shows 'Edit | Remove'; the spec wants Remove/Delete only. Decide keep-as-is or log a fix.</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25989): a processing fee is REMOVE-ONLY on the backend — POST /api/work-orders/adjustments/change on the processing fee returns HTTP 409 'A processing fee cannot be edited through this endpoint', while the same edit on a normal whole-WO fee returns 200. Backend behaviour matches spec S8-N5/S8-R17. The residual deviation is UI-only (the ⋮ menu still OFFERS 'Edit') — the per-fee ⋮ menu could not be isolated headless this run; re-confirm the menu label. Update the backend-enforcement part to Verified.</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>SV-8279 / SV-8284</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Apply update</t>
         </is>
       </c>
     </row>

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -53,12 +53,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 10 of 13 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 12 of 13 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Confirm which permission controls adding or editing a whole-work-order fee/discount — the build may use one single 'edit work order' check instead of the separate whole-WO and line-level permissions the spec describes. Needs a check on staging with a restricted user.</t>
+          <t>LIVE 2026-07-23 (WO S-25989, switch-user impersonation of the Sales Representative role which has workOrdersCreateAndEdit=FALSE): adding a whole-work-order fee returned HTTP 201 — the backend does NOT enforce 'Work Orders: Create &amp; Edit' for adding a whole-WO fee/discount; it is a front-end-only gate. Confirms the deviation (Story 13 maps the action to WO Create&amp;Edit + See Financial Data, but the backend doesn't enforce it). Test data cleaned up; no roles changed.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -574,333 +574,333 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>C28456</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Inline display (Lines tab)</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23: a labor line with 2+ fees/discounts now shows an inline 'Fee 10% +$46.49' row PLUS a 'Show 1 more' / 'Show less' collapse-expand toggle (clicking expands then reads 'Show less'). The collapse control the spec asks for EXISTS — the earlier 'no Show more/less toggle' finding is resolved. Update the case to Verified.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>SV-8279 / SV-8288</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>C28460</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23: the Statistics tab now shows a 'Fees &amp; Discounts (6)' section with PER-ADJUSTMENT rows (columns % and Amount: 'Fee +10% +$46.49', 'Discount', 'Fee −11% −$2.39', etc.) plus a Total — the earlier 'aggregate only, no per-row' finding no longer holds. Still to confirm: whether each row has a scope hyperlink to jump to its item. Update the case to the per-row layout.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>C28462</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (WO S-25989 Statistics tab): fees/discounts are listed OLDEST-FIRST — display order Part Fee, WO Processing Fee, bil matches their creation order (createdAt 14:17:53, 14:17:53, 14:44:25). Matches spec §5-R9; the case (authored to spec) is correct. Part Fee correctly shows $0.00. Mark Verified.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>C28489</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (customer 'Default Fees &amp; Discounts' tab): the defaults TABLE shows full columns — Name, Type, Calculation Type, Amount, Max Amount, Taxable — and a Processing Fee displays with Type 'Fee' (e.g. 'Processing Fee | Fee | % of Grand Total | 6%'), confirming the 'shows as Fee' point. Still to confirm: whether the 'Add Fee/Discount' picker DROPDOWN lists name-only vs columns. Update the case to the observed table display.</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>SV-8284 / SV-8285</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>C28490</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>SV-8285</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>C28511</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Template admin — scoping</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23: the LINE-SCOPE fee dialog now HAS a template picker — the 'New Part Fee / Discount' dialog (and the labour-line one) shows 'Apply From Template' with 'Showing templates compatible with this line', and the whole-WO dialog has it too. The earlier 'no template picker at line scope' deviation is resolved; the scope-filtering hint is present. Update the case to the picker-present, scope-filtered behaviour.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>SV-8278 / SV-8281</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>C28526</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Processing Fee — WO behavior</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (WO S-25989): a processing fee is REMOVE-ONLY on the backend — POST /api/work-orders/adjustments/change on the processing fee returns HTTP 409 'A processing fee cannot be edited through this endpoint', while the same edit on a normal whole-WO fee returns 200. Backend behaviour matches spec S8-N5/S8-R17. The residual deviation is UI-only (the ⋮ menu still OFFERS 'Edit') — the per-fee ⋮ menu could not be isolated headless this run; re-confirm the menu label. Update the backend-enforcement part to Verified.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>SV-8279 / SV-8284</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>C28527</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (WO S-25989, seeded by QA): processing-fee base now EXCLUDES whole-WO fees — FIXED. Numbers: labour $244 + shop supplies $20 = net subtotal $264; ×1.05 GST = Grand Total $277.20; Processing Fee 10% = $27.72 (matches the observed $27.72 to the cent). The whole-WO 'bil' fee ($24.40) is NOT in the base (the old bug would give $30.28). Spec §5-R4 satisfied — the earlier 'base includes whole-WO fees' deviation is resolved. Update the case to Verified.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>SV-8284</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>C28580</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (WO S-25989): same result as C28527 — the Grand-Total base for the Processing Fee correctly excludes whole-WO fees and their tax (10% × ($264 net ×1.05) = $27.72, observed $27.72; buggy would be $30.28). Calculation-contract deviation resolved. Update the case to Verified.</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>SV-7865</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>NOT DONE (Testing QA)</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
@@ -924,7 +924,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
+          <t>LIVE 2026-07-23 (switch-user as Sales Representative, workOrdersCreateAndEdit=FALSE): POST add whole-WO fee → HTTP 201 (not blocked). Whole-WO adjustment add is NOT backend-enforced — front-end-only gate, same finding as C28436. Confirms the permission deviation.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -944,74 +944,74 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>new (SV-8521)</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(no TestRail case yet — to author)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Finance/Invoice — part-line display</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (WO S9-25393 Finance/Estimate view): part-line adjustments DO render as indented child rows under their part — '↳ Name $11.00' and '↳ Fee (% of parts) ($2.39)' show under the T-BOLT CLAMP part, exactly like the labour-line '↳ Fee (% of labor)' / '↳ Discount'. So on the work-order invoice this appears FIXED (matches SV-8521 'Ready for QA'). Still to confirm: the Parts Sale invoice view. Author a case for both surfaces.</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>SV-8521</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>NOT DONE (Ready for QA)</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>New case + verify</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>new (SV-8520)</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>(no TestRail case yet — to author)</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Part line — display after receive/pick</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (WO S-25991, QA-seeded): CONFIRMED — a 50% part fee was added to a part then the part was picked; the part line row now shows $99.00 with NO indented fee child row, yet the line TOTAL is $392.50 (labour $244 + part $99 + the $49.50 fee). So the fee is still billed but hidden from the line after pick — matches SV-8520. Author the case as a confirmed defect (Testing Stage).</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>SV-8520</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>NOT DONE (Testing Stage)</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>New case + verify</t>
         </is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Confirm which permission controls adding or editing a whole-work-order fee/discount — the build may use one single 'edit work order' check instead of the separate whole-WO and line-level permissions the spec describes. Needs a check on staging with a restricted user.</t>
+          <t>LIVE 2026-07-23 (WO S-25989, switch-user impersonation of the Sales Representative role which has workOrdersCreateAndEdit=FALSE): adding a whole-work-order fee returned HTTP 201 — the backend does NOT enforce 'Work Orders: Create &amp; Edit' for adding a whole-WO fee/discount; it is a front-end-only gate. Confirms the deviation (Story 13 maps the action to WO Create&amp;Edit + See Financial Data, but the backend doesn't enforce it). Test data cleaned up; no roles changed.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1129,333 +1129,333 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>C28456</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28456</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Inline display (Lines tab)</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23: a labor line with 2+ fees/discounts now shows an inline 'Fee 10% +$46.49' row PLUS a 'Show 1 more' / 'Show less' collapse-expand toggle (clicking expands then reads 'Show less'). The collapse control the spec asks for EXISTS — the earlier 'no Show more/less toggle' finding is resolved. Update the case to Verified.</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>SV-8279 / SV-8288</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>C28460</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23: the Statistics tab now shows a 'Fees &amp; Discounts (6)' section with PER-ADJUSTMENT rows (columns % and Amount: 'Fee +10% +$46.49', 'Discount', 'Fee −11% −$2.39', etc.) plus a Total — the earlier 'aggregate only, no per-row' finding no longer holds. Still to confirm: whether each row has a scope hyperlink to jump to its item. Update the case to the per-row layout.</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>C28462</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28462</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (WO S-25989 Statistics tab): fees/discounts are listed OLDEST-FIRST — display order Part Fee, WO Processing Fee, bil matches their creation order (createdAt 14:17:53, 14:17:53, 14:44:25). Matches spec §5-R9; the case (authored to spec) is correct. Part Fee correctly shows $0.00. Mark Verified.</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>C28489</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28489</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (customer 'Default Fees &amp; Discounts' tab): the defaults TABLE shows full columns — Name, Type, Calculation Type, Amount, Max Amount, Taxable — and a Processing Fee displays with Type 'Fee' (e.g. 'Processing Fee | Fee | % of Grand Total | 6%'), confirming the 'shows as Fee' point. Still to confirm: whether the 'Add Fee/Discount' picker DROPDOWN lists name-only vs columns. Update the case to the observed table display.</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>SV-8284 / SV-8285</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>C28490</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>SV-8285</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>C28511</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28511</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Template admin — scoping</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23: the LINE-SCOPE fee dialog now HAS a template picker — the 'New Part Fee / Discount' dialog (and the labour-line one) shows 'Apply From Template' with 'Showing templates compatible with this line', and the whole-WO dialog has it too. The earlier 'no template picker at line scope' deviation is resolved; the scope-filtering hint is present. Update the case to the picker-present, scope-filtered behaviour.</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>SV-8278 / SV-8281</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>C28526</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28526</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Processing Fee — WO behavior</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (WO S-25989): a processing fee is REMOVE-ONLY on the backend — POST /api/work-orders/adjustments/change on the processing fee returns HTTP 409 'A processing fee cannot be edited through this endpoint', while the same edit on a normal whole-WO fee returns 200. Backend behaviour matches spec S8-N5/S8-R17. The residual deviation is UI-only (the ⋮ menu still OFFERS 'Edit') — the per-fee ⋮ menu could not be isolated headless this run; re-confirm the menu label. Update the backend-enforcement part to Verified.</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>SV-8279 / SV-8284</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>C28527</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28527</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>Processing Fee — calculation</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (WO S-25989, seeded by QA): processing-fee base now EXCLUDES whole-WO fees — FIXED. Numbers: labour $244 + shop supplies $20 = net subtotal $264; ×1.05 GST = Grand Total $277.20; Processing Fee 10% = $27.72 (matches the observed $27.72 to the cent). The whole-WO 'bil' fee ($24.40) is NOT in the base (the old bug would give $30.28). Spec §5-R4 satisfied — the earlier 'base includes whole-WO fees' deviation is resolved. Update the case to Verified.</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>SV-8284</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>C28580</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28580</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Calculation contract</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (WO S-25989): same result as C28527 — the Grand-Total base for the Processing Fee correctly excludes whole-WO fees and their tax (10% × ($264 net ×1.05) = $27.72, observed $27.72; buggy would be $30.28). Calculation-contract deviation resolved. Update the case to Verified.</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>SV-7865</t>
         </is>
       </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>NOT DONE (Testing QA)</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: Adding a whole-work-order fee/discount is not blocked by the backend for a user without work-order edit rights (the block is front-end only). Confirm the intended enforcement.</t>
+          <t>LIVE 2026-07-23 (switch-user as Sales Representative, workOrdersCreateAndEdit=FALSE): POST add whole-WO fee → HTTP 201 (not blocked). Whole-WO adjustment add is NOT backend-enforced — front-end-only gate, same finding as C28436. Confirms the permission deviation.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1499,74 +1499,74 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>new (SV-8521)</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>(no TestRail case yet — to author)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Finance/Invoice — part-line display</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (WO S9-25393 Finance/Estimate view): part-line adjustments DO render as indented child rows under their part — '↳ Name $11.00' and '↳ Fee (% of parts) ($2.39)' show under the T-BOLT CLAMP part, exactly like the labour-line '↳ Fee (% of labor)' / '↳ Discount'. So on the work-order invoice this appears FIXED (matches SV-8521 'Ready for QA'). Still to confirm: the Parts Sale invoice view. Author a case for both surfaces.</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>SV-8521</t>
         </is>
       </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>NOT DONE (Ready for QA)</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>New case + verify</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>new (SV-8520)</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>(no TestRail case yet — to author)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Part line — display after receive/pick</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>LIVE 2026-07-23 (WO S-25991, QA-seeded): CONFIRMED — a 50% part fee was added to a part then the part was picked; the part line row now shows $99.00 with NO indented fee child row, yet the line TOTAL is $392.50 (labour $244 + part $99 + the $49.50 fee). So the fee is still billed but hidden from the line after pick — matches SV-8520. Author the case as a confirmed defect (Testing Stage).</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>SV-8520</t>
         </is>
       </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>NOT DONE (Testing Stage)</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>New case + verify</t>
         </is>

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -39,7 +39,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,11 +54,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -96,9 +91,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -488,7 +480,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 12 of 13 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 13 of 13 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
         </is>
       </c>
     </row>
@@ -722,37 +714,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>C28490</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (customer with ALL fee templates already linked): the 'Add Fee/Discount' picker dropdown shows 'No results' — confirming the case: the empty state is 'No results', not the spec's 'No templates available to add.' (the PO accepted 'No results' as-is). Case expected message is correct; mark Verified.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>SV-8285</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>
@@ -1277,37 +1269,37 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>C28490</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28490</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Customer Fees &amp; Discounts tab</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>⏳ LIVE CHECK PENDING (2026-07-23 run: not yet observed) — prior finding: When every template is already linked, the dropdown shows 'No results' instead of the spec's 'No templates available to add.' The product owner accepted 'No results' as-is — update the case's expected message to 'No results'.</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (customer with ALL fee templates already linked): the 'Add Fee/Discount' picker dropdown shows 'No results' — confirming the case: the empty state is 'No results', not the spec's 'No templates available to add.' (the PO accepted 'No results' as-is). Case expected message is correct; mark Verified.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>SV-8285</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Apply update</t>
         </is>

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>LIVE 2026-07-23 (WO S-25989, switch-user impersonation of the Sales Representative role which has workOrdersCreateAndEdit=FALSE): adding a whole-work-order fee returned HTTP 201 — the backend does NOT enforce 'Work Orders: Create &amp; Edit' for adding a whole-WO fee/discount; it is a front-end-only gate. Confirms the deviation (Story 13 maps the action to WO Create&amp;Edit + See Financial Data, but the backend doesn't enforce it). Test data cleaned up; no roles changed.</t>
+          <t>LIVE 2026-07-23: the UI hides 'Add Work Order Fee / Discount' for a role without 'Work Orders: Create &amp; Edit' (front-end gate). The same add STILL succeeds through the API — a Sales-Representative-role user (WO Create&amp;Edit = FALSE) POSTed a whole-WO fee and got HTTP 201. Per the rule, this is NOT a bug: the UI behaviour is the tester-facing result; FLAG = 'It can be done through the API though.' Case wording (UI option hidden) stays as-is; no edit needed.</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>FLAG (API-possible)</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>LIVE 2026-07-23 (switch-user as Sales Representative, workOrdersCreateAndEdit=FALSE): POST add whole-WO fee → HTTP 201 (not blocked). Whole-WO adjustment add is NOT backend-enforced — front-end-only gate, same finding as C28436. Confirms the permission deviation.</t>
+          <t>LIVE 2026-07-23 (switch-user as Sales Representative, WO Create&amp;Edit=FALSE): the UI gate hides add/edit/remove, but a direct API add returned HTTP 201 — front-end-only gate. Not a bug (Rule 24): FLAG 'can be done through the API'. The case's tester-facing 'action is refused' should read as the UI control being hidden; the backend non-enforcement is a flagged note, not a Deviation.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -931,19 +931,19 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>FLAG (API-possible)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>new (SV-8521)</t>
+          <t>C30639</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>(no TestRail case yet — to author)</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30639</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -975,12 +975,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>new (SV-8520)</t>
+          <t>C30640</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>(no TestRail case yet — to author)</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30640</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>LIVE 2026-07-23 (WO S-25989, switch-user impersonation of the Sales Representative role which has workOrdersCreateAndEdit=FALSE): adding a whole-work-order fee returned HTTP 201 — the backend does NOT enforce 'Work Orders: Create &amp; Edit' for adding a whole-WO fee/discount; it is a front-end-only gate. Confirms the deviation (Story 13 maps the action to WO Create&amp;Edit + See Financial Data, but the backend doesn't enforce it). Test data cleaned up; no roles changed.</t>
+          <t>LIVE 2026-07-23: the UI hides 'Add Work Order Fee / Discount' for a role without 'Work Orders: Create &amp; Edit' (front-end gate). The same add STILL succeeds through the API — a Sales-Representative-role user (WO Create&amp;Edit = FALSE) POSTed a whole-WO fee and got HTTP 201. Per the rule, this is NOT a bug: the UI behaviour is the tester-facing result; FLAG = 'It can be done through the API though.' Case wording (UI option hidden) stays as-is; no edit needed.</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>FLAG (API-possible)</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>LIVE 2026-07-23 (switch-user as Sales Representative, workOrdersCreateAndEdit=FALSE): POST add whole-WO fee → HTTP 201 (not blocked). Whole-WO adjustment add is NOT backend-enforced — front-end-only gate, same finding as C28436. Confirms the permission deviation.</t>
+          <t>LIVE 2026-07-23 (switch-user as Sales Representative, WO Create&amp;Edit=FALSE): the UI gate hides add/edit/remove, but a direct API add returned HTTP 201 — front-end-only gate. Not a bug (Rule 24): FLAG 'can be done through the API'. The case's tester-facing 'action is refused' should read as the UI control being hidden; the backend non-enforcement is a flagged note, not a Deviation.</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>DECISION</t>
+          <t>FLAG (API-possible)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>new (SV-8521)</t>
+          <t>C30639</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>(no TestRail case yet — to author)</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30639</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1530,12 +1530,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>new (SV-8520)</t>
+          <t>C30640</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>(no TestRail case yet — to author)</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/30640</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -39,7 +39,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,7 +88,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,6 +96,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -480,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 13 of 13 rows re-verified live on staging (green); 0 characterised-blocked on an env defect (orange, see column D); the rest flagged '⏳ LIVE CHECK PENDING'.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 12 of 13 rows re-verified live (green); 1 confirmed DEVIATION needing a decision; 0 env-blocked; the rest flagged '⏳ LIVE CHECK PENDING'.</t>
         </is>
       </c>
     </row>
@@ -603,39 +611,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>C28460</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23: the Statistics tab now shows a 'Fees &amp; Discounts (6)' section with PER-ADJUSTMENT rows (columns % and Amount: 'Fee +10% +$46.49', 'Discount', 'Fee −11% −$2.39', etc.) plus a Total — the earlier 'aggregate only, no per-row' finding no longer holds. Still to confirm: whether each row has a scope hyperlink to jump to its item. Update the case to the per-row layout.</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25991 Statistics tab, has a line-level part fee 'pp'): the 'Fees &amp; Discounts' section shows PER-ADJUSTMENT rows with the fee NAME + % + Amount ('Part Fee +11% +$16.34', 'pp +50% +$49.50', Total), BUT the row does NOT name its target line/part and there is NO per-row clickable link to jump to the item (the only links on the page are the Lines/Parts tabs). The case expects each row to name its target AND be a clickable link → DEVIATION: build shows the fee name only. Decide: keep the case as design-intent + log a fix, or accept the shipped display.</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Apply update</t>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>DECISION</t>
         </is>
       </c>
     </row>
@@ -1158,39 +1166,39 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>C28460</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23: the Statistics tab now shows a 'Fees &amp; Discounts (6)' section with PER-ADJUSTMENT rows (columns % and Amount: 'Fee +10% +$46.49', 'Discount', 'Fee −11% −$2.39', etc.) plus a Total — the earlier 'aggregate only, no per-row' finding no longer holds. Still to confirm: whether each row has a scope hyperlink to jump to its item. Update the case to the per-row layout.</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>LIVE 2026-07-23 (WO S-25991 Statistics tab, has a line-level part fee 'pp'): the 'Fees &amp; Discounts' section shows PER-ADJUSTMENT rows with the fee NAME + % + Amount ('Part Fee +11% +$16.34', 'pp +50% +$49.50', Total), BUT the row does NOT name its target line/part and there is NO per-row clickable link to jump to the item (the only links on the page are the Lines/Parts tabs). The case expects each row to name its target AND be a clickable link → DEVIATION: build shows the fee name only. Decide: keep the case as design-intent + log a fix, or accept the shipped display.</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Apply update</t>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>DECISION</t>
         </is>
       </c>
     </row>

--- a/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
+++ b/build/fees-discounts/FeesAndDiscounts_SpecRecheck_ChangeList_2026-07-23.xlsx
@@ -39,7 +39,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,11 +54,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -96,9 +91,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -488,7 +480,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LIVE-BUILD CHECK 2026-07-23: 12 of 13 rows re-verified live (green); 1 confirmed DEVIATION needing a decision; 0 env-blocked; the rest flagged '⏳ LIVE CHECK PENDING'.</t>
+          <t>LIVE-BUILD CHECK 2026-07-23: 13 of 13 rows re-verified live (green); 0 confirmed DEVIATION needing a decision; 0 env-blocked; the rest flagged '⏳ LIVE CHECK PENDING'.</t>
         </is>
       </c>
     </row>
@@ -611,39 +603,39 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>C28460</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23 (WO S-25991 Statistics tab, has a line-level part fee 'pp'): the 'Fees &amp; Discounts' section shows PER-ADJUSTMENT rows with the fee NAME + % + Amount ('Part Fee +11% +$16.34', 'pp +50% +$49.50', Total), BUT the row does NOT name its target line/part and there is NO per-row clickable link to jump to the item (the only links on the page are the Lines/Parts tabs). The case expects each row to name its target AND be a clickable link → DEVIATION: build shows the fee name only. Decide: keep the case as design-intent + log a fix, or accept the shipped display.</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>UPDATED 2026-07-23 (update_case 200) — matched to the build per user. The Statistics 'Fees &amp; Discounts' section shows each adjustment as a row with NAME + % + Amount + Total ('Part Fee +11% +$16.34', 'pp +50% +$49.50'), $0.00 for zero-value; it does NOT show a per-row target line/part or clickable link. The target/link was DESIGN-ONLY (design §3) — the FD spec only requires adjustments to 'appear on the Statistics tab' (§3) 'oldest first' (§5-R9), so the build is spec-compliant. Case reworded to the shipped display; not a bug.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Applied (matched to build)</t>
         </is>
       </c>
     </row>
@@ -1166,39 +1158,39 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>C28460</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/28460</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Statistics tab</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>LIVE 2026-07-23 (WO S-25991 Statistics tab, has a line-level part fee 'pp'): the 'Fees &amp; Discounts' section shows PER-ADJUSTMENT rows with the fee NAME + % + Amount ('Part Fee +11% +$16.34', 'pp +50% +$49.50', Total), BUT the row does NOT name its target line/part and there is NO per-row clickable link to jump to the item (the only links on the page are the Lines/Parts tabs). The case expects each row to name its target AND be a clickable link → DEVIATION: build shows the fee name only. Decide: keep the case as design-intent + log a fix, or accept the shipped display.</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>UPDATED 2026-07-23 (update_case 200) — matched to the build per user. The Statistics 'Fees &amp; Discounts' section shows each adjustment as a row with NAME + % + Amount + Total ('Part Fee +11% +$16.34', 'pp +50% +$49.50'), $0.00 for zero-value; it does NOT show a per-row target line/part or clickable link. The target/link was DESIGN-ONLY (design §3) — the FD spec only requires adjustments to 'appear on the Statistics tab' (§3) 'oldest first' (§5-R9), so the build is spec-compliant. Case reworded to the shipped display; not a bug.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>SV-8280</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>NOT DONE (Open)</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>DECISION</t>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>NOT DONE (Open)</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Applied (matched to build)</t>
         </is>
       </c>
     </row>
